--- a/stella/test_fixtures/strong_promo/stars_data.xlsx
+++ b/stella/test_fixtures/strong_promo/stars_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,23 +485,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>35.6</v>
+        <v>42.27</v>
       </c>
       <c r="E2" t="n">
         <v>12</v>
       </c>
       <c r="F2" t="n">
-        <v>427.18</v>
+        <v>507.27</v>
       </c>
       <c r="G2" t="n">
-        <v>6.32</v>
+        <v>7.47</v>
       </c>
       <c r="H2" t="n">
-        <v>2032.9</v>
+        <v>999.3</v>
       </c>
     </row>
     <row r="3">
@@ -515,28 +515,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34.96</v>
+        <v>41.15</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>419.47</v>
+        <v>493.8</v>
       </c>
       <c r="G3" t="n">
-        <v>6.39</v>
+        <v>7.27</v>
       </c>
       <c r="H3" t="n">
-        <v>2056.3</v>
+        <v>968.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45668</v>
+        <v>45661</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.15</v>
+        <v>41.02</v>
       </c>
       <c r="E4" t="n">
         <v>12</v>
       </c>
       <c r="F4" t="n">
-        <v>409.85</v>
+        <v>492.27</v>
       </c>
       <c r="G4" t="n">
-        <v>6.22</v>
+        <v>7.37</v>
       </c>
       <c r="H4" t="n">
-        <v>2069.6</v>
+        <v>995.1</v>
       </c>
     </row>
     <row r="5">
@@ -575,28 +575,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.68</v>
+        <v>41.86</v>
       </c>
       <c r="E5" t="n">
         <v>12</v>
       </c>
       <c r="F5" t="n">
-        <v>416.18</v>
+        <v>502.35</v>
       </c>
       <c r="G5" t="n">
-        <v>6.15</v>
+        <v>7.4</v>
       </c>
       <c r="H5" t="n">
-        <v>2064.6</v>
+        <v>993.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45675</v>
+        <v>45668</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -605,28 +605,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59.88</v>
+        <v>42.11</v>
       </c>
       <c r="E6" t="n">
         <v>12</v>
       </c>
       <c r="F6" t="n">
-        <v>718.52</v>
+        <v>505.29</v>
       </c>
       <c r="G6" t="n">
-        <v>10.62</v>
+        <v>7.45</v>
       </c>
       <c r="H6" t="n">
-        <v>2388</v>
+        <v>981.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45675</v>
+        <v>45668</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -635,28 +635,28 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59.35</v>
+        <v>41.5</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
       </c>
       <c r="F7" t="n">
-        <v>712.1799999999999</v>
+        <v>498.05</v>
       </c>
       <c r="G7" t="n">
-        <v>10.69</v>
+        <v>7.41</v>
       </c>
       <c r="H7" t="n">
-        <v>2683.8</v>
+        <v>977.8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45682</v>
+        <v>45675</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -665,28 +665,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>61.6</v>
+        <v>54.88</v>
       </c>
       <c r="E8" t="n">
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>739.17</v>
+        <v>658.58</v>
       </c>
       <c r="G8" t="n">
-        <v>10.95</v>
+        <v>9.68</v>
       </c>
       <c r="H8" t="n">
-        <v>3005.8</v>
+        <v>1146.7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45682</v>
+        <v>45675</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -695,28 +695,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>62.25</v>
+        <v>56.85</v>
       </c>
       <c r="E9" t="n">
         <v>12</v>
       </c>
       <c r="F9" t="n">
-        <v>747.0599999999999</v>
+        <v>682.24</v>
       </c>
       <c r="G9" t="n">
-        <v>11.31</v>
+        <v>10.03</v>
       </c>
       <c r="H9" t="n">
-        <v>3331.8</v>
+        <v>1169.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45689</v>
+        <v>45675</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36.27</v>
+        <v>55.2</v>
       </c>
       <c r="E10" t="n">
         <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>435.29</v>
+        <v>662.4400000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>6.64</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>2828.8</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45689</v>
+        <v>45682</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -755,28 +755,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>36.8</v>
+        <v>56.49</v>
       </c>
       <c r="E11" t="n">
         <v>12</v>
       </c>
       <c r="F11" t="n">
-        <v>441.65</v>
+        <v>677.88</v>
       </c>
       <c r="G11" t="n">
-        <v>6.62</v>
+        <v>10.31</v>
       </c>
       <c r="H11" t="n">
-        <v>2311.7</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45696</v>
+        <v>45682</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -785,28 +785,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38.76</v>
+        <v>54.47</v>
       </c>
       <c r="E12" t="n">
         <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>465.16</v>
+        <v>653.58</v>
       </c>
       <c r="G12" t="n">
-        <v>6.92</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1797.4</v>
+        <v>1322.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45696</v>
+        <v>45682</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -815,28 +815,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>35.98</v>
+        <v>56.06</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
       </c>
       <c r="F13" t="n">
-        <v>431.74</v>
+        <v>672.72</v>
       </c>
       <c r="G13" t="n">
-        <v>6.49</v>
+        <v>9.98</v>
       </c>
       <c r="H13" t="n">
-        <v>1230.1</v>
+        <v>1293.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45703</v>
+        <v>45689</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -845,28 +845,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36.22</v>
+        <v>114.3</v>
       </c>
       <c r="E14" t="n">
         <v>12</v>
       </c>
       <c r="F14" t="n">
-        <v>434.65</v>
+        <v>1371.66</v>
       </c>
       <c r="G14" t="n">
-        <v>6.43</v>
+        <v>20.2</v>
       </c>
       <c r="H14" t="n">
-        <v>688</v>
+        <v>1484.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45703</v>
+        <v>45689</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>38.79</v>
+        <v>112.37</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>465.54</v>
+        <v>1348.44</v>
       </c>
       <c r="G15" t="n">
-        <v>7.01</v>
+        <v>19.94</v>
       </c>
       <c r="H15" t="n">
-        <v>200</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45710</v>
+        <v>45689</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -905,28 +905,28 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38.31</v>
+        <v>107.3</v>
       </c>
       <c r="E16" t="n">
         <v>12</v>
       </c>
       <c r="F16" t="n">
-        <v>459.73</v>
+        <v>1287.62</v>
       </c>
       <c r="G16" t="n">
-        <v>6.89</v>
+        <v>19.64</v>
       </c>
       <c r="H16" t="n">
-        <v>200</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45710</v>
+        <v>45696</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -935,28 +935,28 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>35.96</v>
+        <v>107.74</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>431.49</v>
+        <v>1292.94</v>
       </c>
       <c r="G17" t="n">
-        <v>6.37</v>
+        <v>19.03</v>
       </c>
       <c r="H17" t="n">
-        <v>200</v>
+        <v>1605.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45717</v>
+        <v>45696</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -965,28 +965,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>34.81</v>
+        <v>111.56</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>417.69</v>
+        <v>1338.75</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2</v>
+        <v>19.87</v>
       </c>
       <c r="H18" t="n">
-        <v>262.5</v>
+        <v>1611.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45717</v>
+        <v>45696</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -995,28 +995,28 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>34.29</v>
+        <v>111.3</v>
       </c>
       <c r="E19" t="n">
         <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>411.46</v>
+        <v>1335.57</v>
       </c>
       <c r="G19" t="n">
-        <v>6.26</v>
+        <v>20.31</v>
       </c>
       <c r="H19" t="n">
-        <v>326.9</v>
+        <v>1513.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45724</v>
+        <v>45703</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1025,28 +1025,28 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>33.76</v>
+        <v>113.62</v>
       </c>
       <c r="E20" t="n">
         <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>405.15</v>
+        <v>1363.49</v>
       </c>
       <c r="G20" t="n">
-        <v>6.05</v>
+        <v>20.55</v>
       </c>
       <c r="H20" t="n">
-        <v>383.2</v>
+        <v>1796.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45724</v>
+        <v>45703</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>34.41</v>
+        <v>112.91</v>
       </c>
       <c r="E21" t="n">
         <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>412.96</v>
+        <v>1354.95</v>
       </c>
       <c r="G21" t="n">
-        <v>6.29</v>
+        <v>20.61</v>
       </c>
       <c r="H21" t="n">
-        <v>451.9</v>
+        <v>1777.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45731</v>
+        <v>45703</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1085,28 +1085,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>33.31</v>
+        <v>114.2</v>
       </c>
       <c r="E22" t="n">
         <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>399.77</v>
+        <v>1370.43</v>
       </c>
       <c r="G22" t="n">
-        <v>5.93</v>
+        <v>20.52</v>
       </c>
       <c r="H22" t="n">
-        <v>487</v>
+        <v>1687.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45731</v>
+        <v>45710</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1115,28 +1115,28 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34.86</v>
+        <v>114.78</v>
       </c>
       <c r="E23" t="n">
         <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>418.33</v>
+        <v>1377.41</v>
       </c>
       <c r="G23" t="n">
-        <v>6.18</v>
+        <v>20.55</v>
       </c>
       <c r="H23" t="n">
-        <v>532.1</v>
+        <v>1943.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45738</v>
+        <v>45710</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>34.26</v>
+        <v>108.89</v>
       </c>
       <c r="E24" t="n">
         <v>12</v>
       </c>
       <c r="F24" t="n">
-        <v>411.08</v>
+        <v>1306.74</v>
       </c>
       <c r="G24" t="n">
-        <v>6.08</v>
+        <v>19.84</v>
       </c>
       <c r="H24" t="n">
-        <v>589.6</v>
+        <v>1834.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45738</v>
+        <v>45710</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1175,28 +1175,28 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>33.48</v>
+        <v>107.99</v>
       </c>
       <c r="E25" t="n">
         <v>12</v>
       </c>
       <c r="F25" t="n">
-        <v>401.81</v>
+        <v>1295.91</v>
       </c>
       <c r="G25" t="n">
-        <v>5.94</v>
+        <v>19.37</v>
       </c>
       <c r="H25" t="n">
-        <v>616.1</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45745</v>
+        <v>45717</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1205,28 +1205,28 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.09</v>
+        <v>34.91</v>
       </c>
       <c r="E26" t="n">
         <v>12</v>
       </c>
       <c r="F26" t="n">
-        <v>397.08</v>
+        <v>418.87</v>
       </c>
       <c r="G26" t="n">
-        <v>5.9</v>
+        <v>6.16</v>
       </c>
       <c r="H26" t="n">
-        <v>602.1</v>
+        <v>1951.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45745</v>
+        <v>45717</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1235,28 +1235,28 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>32.95</v>
+        <v>34.74</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>395.45</v>
+        <v>416.82</v>
       </c>
       <c r="G27" t="n">
-        <v>5.82</v>
+        <v>6.17</v>
       </c>
       <c r="H27" t="n">
-        <v>610.6</v>
+        <v>1840.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45752</v>
+        <v>45717</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1265,28 +1265,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>33.12</v>
+        <v>36.73</v>
       </c>
       <c r="E28" t="n">
         <v>12</v>
       </c>
       <c r="F28" t="n">
-        <v>397.38</v>
+        <v>440.72</v>
       </c>
       <c r="G28" t="n">
-        <v>5.85</v>
+        <v>6.67</v>
       </c>
       <c r="H28" t="n">
-        <v>624.1</v>
+        <v>1770.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45752</v>
+        <v>45724</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1295,28 +1295,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>34.49</v>
+        <v>37.25</v>
       </c>
       <c r="E29" t="n">
         <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>413.9</v>
+        <v>447.03</v>
       </c>
       <c r="G29" t="n">
-        <v>6.18</v>
+        <v>6.73</v>
       </c>
       <c r="H29" t="n">
-        <v>636.9</v>
+        <v>1973.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45759</v>
+        <v>45724</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1325,28 +1325,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Sensitivity 4oz</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>34.01</v>
+        <v>35.1</v>
       </c>
       <c r="E30" t="n">
         <v>12</v>
       </c>
       <c r="F30" t="n">
-        <v>408.15</v>
+        <v>421.14</v>
       </c>
       <c r="G30" t="n">
-        <v>6.21</v>
+        <v>6.37</v>
       </c>
       <c r="H30" t="n">
-        <v>652.6</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45759</v>
+        <v>45724</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1355,28 +1355,28 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SF-Variety 12ct</t>
+          <t>SF-Complete 6oz</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>32.76</v>
+        <v>36.15</v>
       </c>
       <c r="E31" t="n">
         <v>12</v>
       </c>
       <c r="F31" t="n">
-        <v>393.1</v>
+        <v>433.75</v>
       </c>
       <c r="G31" t="n">
-        <v>5.82</v>
+        <v>6.63</v>
       </c>
       <c r="H31" t="n">
-        <v>636.8</v>
+        <v>1783.9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45766</v>
+        <v>45731</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1385,53 +1385,533 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SF-Original 12ct</t>
+          <t>SF-Whitening 6oz</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>33.32</v>
+        <v>36.77</v>
       </c>
       <c r="E32" t="n">
         <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>399.82</v>
+        <v>441.25</v>
       </c>
       <c r="G32" t="n">
-        <v>6.01</v>
+        <v>6.75</v>
       </c>
       <c r="H32" t="n">
-        <v>646.9</v>
+        <v>1975.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>37.11</v>
+      </c>
+      <c r="E33" t="n">
+        <v>12</v>
+      </c>
+      <c r="F33" t="n">
+        <v>445.3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1828.4</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45731</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>38.36</v>
+      </c>
+      <c r="E34" t="n">
+        <v>12</v>
+      </c>
+      <c r="F34" t="n">
+        <v>460.33</v>
+      </c>
+      <c r="G34" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1773.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>36.87</v>
+      </c>
+      <c r="E35" t="n">
+        <v>12</v>
+      </c>
+      <c r="F35" t="n">
+        <v>442.5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1945.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12</v>
+      </c>
+      <c r="F36" t="n">
+        <v>465.01</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1819.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>45738</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>38.54</v>
+      </c>
+      <c r="E37" t="n">
+        <v>12</v>
+      </c>
+      <c r="F37" t="n">
+        <v>462.51</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1772.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>41.66</v>
+      </c>
+      <c r="E38" t="n">
+        <v>12</v>
+      </c>
+      <c r="F38" t="n">
+        <v>499.95</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1922.7</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="E39" t="n">
+        <v>12</v>
+      </c>
+      <c r="F39" t="n">
+        <v>505.76</v>
+      </c>
+      <c r="G39" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1815.2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>45745</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="E40" t="n">
+        <v>12</v>
+      </c>
+      <c r="F40" t="n">
+        <v>512.73</v>
+      </c>
+      <c r="G40" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1768.5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="E41" t="n">
+        <v>12</v>
+      </c>
+      <c r="F41" t="n">
+        <v>506.71</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>43.51</v>
+      </c>
+      <c r="E42" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" t="n">
+        <v>522.08</v>
+      </c>
+      <c r="G42" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1839.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>45752</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="E43" t="n">
+        <v>12</v>
+      </c>
+      <c r="F43" t="n">
+        <v>493.44</v>
+      </c>
+      <c r="G43" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1748.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="E44" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" t="n">
+        <v>517.45</v>
+      </c>
+      <c r="G44" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1891.2</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="E45" t="n">
+        <v>12</v>
+      </c>
+      <c r="F45" t="n">
+        <v>496.88</v>
+      </c>
+      <c r="G45" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1794.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45759</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>12</v>
+      </c>
+      <c r="F46" t="n">
+        <v>526.83</v>
+      </c>
+      <c r="G46" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1737.4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
         <v>45766</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Summit Foods</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>SF-Variety 12ct</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>32.77</v>
-      </c>
-      <c r="E33" t="n">
-        <v>12</v>
-      </c>
-      <c r="F33" t="n">
-        <v>393.29</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="H33" t="n">
-        <v>644.9</v>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SF-Whitening 6oz</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="E47" t="n">
+        <v>12</v>
+      </c>
+      <c r="F47" t="n">
+        <v>519.53</v>
+      </c>
+      <c r="G47" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SF-Sensitivity 4oz</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12</v>
+      </c>
+      <c r="F48" t="n">
+        <v>510.69</v>
+      </c>
+      <c r="G48" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1787.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45766</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Summit Foods</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SF-Complete 6oz</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="E49" t="n">
+        <v>12</v>
+      </c>
+      <c r="F49" t="n">
+        <v>521.54</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1726.5</v>
       </c>
     </row>
   </sheetData>
